--- a/Test.xlsx
+++ b/Test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25330"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ms90982\Desktop\Python\BloodTestAnalysis\Python\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Projects\BloodTestAnalyzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7506F33-33FE-4396-80E7-B8A31BECE2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1547CB81-3B96-4B56-BC41-FB7D187CB158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5835" yWindow="1410" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Number" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,9 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -114,24 +117,12 @@
     <t>06/06/1393</t>
   </si>
   <si>
-    <t>Baqiatollah Hospital</t>
-  </si>
-  <si>
-    <t>Mr. Ghodratollah Faraji</t>
-  </si>
-  <si>
     <t>25/12/1393</t>
   </si>
   <si>
-    <t>Mr. Ebrahim Malek Mohammadi</t>
-  </si>
-  <si>
     <t>02/06/1394</t>
   </si>
   <si>
-    <t>Ms. Javad Vafadar</t>
-  </si>
-  <si>
     <t>24/05/1396</t>
   </si>
   <si>
@@ -181,6 +172,18 @@
   </si>
   <si>
     <t>09/03/1401</t>
+  </si>
+  <si>
+    <t>Ba Hospital</t>
+  </si>
+  <si>
+    <t>Mr.  Faraji</t>
+  </si>
+  <si>
+    <t>Mr.  Mohammadi</t>
+  </si>
+  <si>
+    <t>Ms.  Vafadar</t>
   </si>
 </sst>
 </file>
@@ -195,7 +198,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -207,7 +210,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1864,25 +1867,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AA12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="5" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="9" width="4" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.625" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="4" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="3.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="3.625" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="4" style="16" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.42578125" style="16" customWidth="1"/>
-    <col min="19" max="27" width="3.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="4.375" style="16" customWidth="1"/>
+    <col min="19" max="27" width="3.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.625" style="1" customWidth="1"/>
     <col min="29" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="6" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" s="6" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="21" t="s">
         <v>24</v>
       </c>
@@ -1965,15 +1968,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="23" t="s">
         <v>27</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="D2" s="18">
         <v>80</v>
@@ -2048,15 +2051,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="23" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="D3" s="17">
         <v>80</v>
@@ -2131,15 +2134,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="23" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D4" s="17">
         <v>80</v>
@@ -2214,15 +2217,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="23" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D5" s="17">
         <v>80.5</v>
@@ -2291,15 +2294,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="23" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D6" s="17">
         <v>80.5</v>
@@ -2374,15 +2377,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="23" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D7" s="17">
         <v>80</v>
@@ -2451,15 +2454,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="27" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D8" s="17">
         <v>80</v>
@@ -2498,15 +2501,15 @@
       <c r="Z8" s="5"/>
       <c r="AA8" s="5"/>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="27" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D9" s="17">
         <v>80</v>
@@ -2581,15 +2584,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="23" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D10" s="19">
         <v>80</v>
@@ -2664,15 +2667,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="23" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D11" s="17">
         <v>80</v>
@@ -2723,15 +2726,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="23" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D12" s="17">
         <v>80</v>
@@ -2802,44 +2805,44 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="F2:F9">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="notBetween">
+      <formula>D2</formula>
+      <formula>E2</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="between">
+      <formula>D2</formula>
+      <formula>E2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F9">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="notBetween">
+      <formula>D9</formula>
+      <formula>E9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="between">
+      <formula>D9</formula>
+      <formula>E9</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I2:I12 L2:L12 O2:O12 R2:R12 U2:U12 X2:X12 AA2:AA12">
-    <cfRule type="cellIs" dxfId="7" priority="15" operator="notBetween">
+    <cfRule type="cellIs" dxfId="3" priority="15" operator="notBetween">
       <formula>G2</formula>
       <formula>H2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="16" operator="between">
+    <cfRule type="cellIs" dxfId="2" priority="16" operator="between">
       <formula>G2</formula>
       <formula>H2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9 L9 O9 R9 U9 X9 AA9">
-    <cfRule type="cellIs" dxfId="5" priority="11" operator="notBetween">
+    <cfRule type="cellIs" dxfId="1" priority="11" operator="notBetween">
       <formula>G9</formula>
       <formula>H9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="12" operator="between">
+    <cfRule type="cellIs" dxfId="0" priority="12" operator="between">
       <formula>G9</formula>
       <formula>H9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F9">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="notBetween">
-      <formula>D2</formula>
-      <formula>E2</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="between">
-      <formula>D2</formula>
-      <formula>E2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="notBetween">
-      <formula>D9</formula>
-      <formula>E9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="between">
-      <formula>D9</formula>
-      <formula>E9</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions verticalCentered="1"/>
